--- a/results/nyff64_films_with_chinese.xlsx
+++ b/results/nyff64_films_with_chinese.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,7 +37,15 @@
       <color rgb="FF0070C0"/>
     </font>
     <font>
+      <b val="1"/>
+      <color rgb="FFCC6600"/>
+    </font>
+    <font>
       <color rgb="FF0070C0"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="FFCC6600"/>
     </font>
   </fonts>
   <fills count="2">
@@ -60,18 +68,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -439,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:I72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -449,7 +461,8 @@
     <col width="46" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -488,24 +501,29 @@
           <t>Famous Actors &amp; Work (Chinese)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Lookup Pending (retry next run)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Sessions</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>PAPER TIGER</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>James Gray</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -564,23 +582,24 @@
           </r>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>Adam Driver: Star Wars: Episode VII – The Force Awakens, Star Wars: Episode VIII – The Last Jedi, Lincoln
 Scarlett Johansson: The Avengers, Avengers: Endgame, Avengers: Infinity War
 Miles Teller: Whiplash, Fantastic Four, Michael</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>亚当·德赖弗: 星球大战：原力觉醒, STAR WARS：最後的絕地武士, 林肯
 斯嘉丽·约翰逊: 復仇者聯盟, 复仇者联盟4, 复仇者联盟3：无限战争
 麥爾斯·泰勒: 爆裂鼓手, 驚奇4超人, 麥可傑克森</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr"/>
-      <c r="G2" s="6" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr"/>
+      <c r="G2" s="7" t="inlineStr"/>
+      <c r="H2" s="8" t="inlineStr"/>
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>6:00 PM Q&amp;A: James Gray, Adam Driver, Scarlett Johansson, Miles Teller
 6:30 PM INTRO: James Gray
@@ -589,17 +608,17 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>BEHEMOTH!</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Tony Gilroy</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -655,27 +674,28 @@
           </r>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>Pedro Pascal: Game of Thrones, The Last of Us, The Mentalist</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>佩德罗·帕斯卡: 权力的游戏, 最后生还者, 超感神探</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>Will Arnett: Men in Black 3</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
-        <is>
-          <t>Will Arnett: 黑衣人3</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>威尔·阿奈特: 黑衣人3</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>6:15 PM Q&amp;A: Tony Gilroy, Pedro Pascal, Will Arnett, Eva Victor
 6:30 PM INTRO: Tony Gilroy, Pedro Pascal
@@ -685,26 +705,27 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>14TH</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Ava DuVernay</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Ava DuVernay; Sherrilyn Ifill; Van Lathan</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr"/>
-      <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr"/>
+      <c r="F4" s="7" t="inlineStr"/>
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>6:00 PM Q&amp;A: Ava DuVernay, Sherrilyn Ifill, Van Lathan
 6:30 PM INTRO: Ava DuVernay
@@ -713,26 +734,27 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>9 TEMPLES TO HEAVEN</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Sompot Chidgasornpongse</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Sompot Chidgasornpongse; Kissada Kamyoung</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr"/>
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>9:00 PM Q&amp;A: Sompot Chidgasornpongse, Kissada Kamyoung
 3:15 PM Q&amp;A: Sompot Chidgasornpongse, Kissada Kamyoung</t>
@@ -740,17 +762,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>ALL OF A SUDDEN</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Ryûsuke Hamaguchi</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -776,19 +798,20 @@
           </r>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Virginie Efira: Elle</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
-        <is>
-          <t>Virginie Efira: 她</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>维尔日妮·埃菲拉: 她</t>
+        </is>
+      </c>
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>5:00 PM Q&amp;A: Ryûsuke Hamaguchi, Virginie Efira
 2:00 PM Q&amp;A: Ryûsuke Hamaguchi, Virginie Efira</t>
@@ -796,26 +819,27 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>ARTIFICIAL</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Luca Guadagnino</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Luca Guadagnino</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="8" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>5:00 PM Q&amp;A: Luca Guadagnino
 2:30 PM Q&amp;A: Luca Guadagnino</t>
@@ -823,17 +847,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>BITTER CHRISTMAS</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Pedro Almodóvar</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -860,19 +884,20 @@
           </r>
         </is>
       </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>Pedro Almodóvar: All About My Mother, All About My Mother, Talk to Her</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>佩德罗·阿尔莫多瓦尔: 关于我母亲的一切, 关于我母亲的一切, 对她说</t>
-        </is>
-      </c>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Pedro Almodóvar: All About My Mother, All About My Mother, Volver</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>佩德罗·阿尔莫多瓦尔: 关于我母亲的一切, 关于我母亲的一切, 回归</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="8" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>5:30 PM Q&amp;A: Pedro Almodóvar, Milena Smit
 3:15 PM Q&amp;A: Pedro Almodóvar, Milena Smit</t>
@@ -880,26 +905,136 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>CLARISSA</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Arie Esiri and Chuko Esiri</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Chuko Esiri; Arie Esiri; Sophie Okonedo; David Oyelowo; India Amarteifio; Toheeb Jimoh; Nina Gold</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Chuko Esiri</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Arie Esiri</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="FF0070C0"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Sophie Okonedo</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="FF008000"/>
+              <sz val="11"/>
+            </rPr>
+            <t>David Oyelowo</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>India Amarteifio</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Toheeb Jimoh</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Nina Gold</t>
+          </r>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>David Oyelowo: Interstellar, The Help, Lincoln</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>大衛·奧伊羅: 星际穿越, 相助, 林肯</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Sophie Okonedo: Hotel Rwanda</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>蘇菲·奧克尼多: 卢旺达饭店</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>5:45 PM Q&amp;A: Chuko Esiri, Arie Esiri, Sophie Okonedo, David Oyelowo, India Amarteifio, Toheeb Jimoh, Nina Gold
 12:00 PM Q&amp;A: Chuko Esiri, Arie Esiri, Sophie Okonedo, David Oyelowo, India Amarteifio, Toheeb Jimoh, Nina Gold</t>
@@ -907,26 +1042,27 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>DAO</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Alain Gomis</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Alain Gomis</t>
         </is>
       </c>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="6" t="inlineStr"/>
-      <c r="G10" s="6" t="inlineStr"/>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="8" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>12:00 PM Q&amp;A: Alain Gomis
 3:00 PM Q&amp;A: Alain Gomis</t>
@@ -934,26 +1070,27 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>DOUBLE FREEDOM</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Lisandro Alonso</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Lisandro Alonso</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="6" t="inlineStr"/>
-      <c r="G11" s="6" t="inlineStr"/>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="D11" s="6" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="8" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>8:30 PM Q&amp;A: Lisandro Alonso
 6:15 PM Q&amp;A: Lisandro Alonso</t>
@@ -961,26 +1098,27 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>THE DREAMED ADVENTURE</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Valeska Grisebach</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Valeska Grisebach</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="6" t="inlineStr"/>
-      <c r="G12" s="6" t="inlineStr"/>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr"/>
+      <c r="E12" s="6" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="7" t="inlineStr"/>
+      <c r="H12" s="8" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>8:15 PM Q&amp;A: Valeska Grisebach
 5:30 PM Q&amp;A: Valeska Grisebach</t>
@@ -988,26 +1126,27 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>EVERYTHING ELSE IS NOISE</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Nicolás Pereda</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Nicolás Pereda; Lázaro G. Rodríguez</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="D13" s="6" t="inlineStr"/>
+      <c r="E13" s="6" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="8" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>4:30 PM Q&amp;A: Nicolás Pereda, Lázaro G. Rodríguez
 9:30 PM Q&amp;A: Nicolás Pereda, Lázaro G. Rodríguez</t>
@@ -1015,26 +1154,27 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>EVERYTIME</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Sandra Wollner</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Sandra Wollner; Carla Hüttermann</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="D14" s="6" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr"/>
+      <c r="H14" s="8" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>9:00 PM Q&amp;A: Sandra Wollner, Carla Hüttermann
 12:45 PM Q&amp;A: Sandra Wollner, Carla Hüttermann</t>
@@ -1042,26 +1182,56 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>FATHERLAND</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Paweł Pawlikowski</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>Paweł Pawlikowski; Hanns Zischler</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr"/>
-      <c r="E15" s="5" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Paweł Pawlikowski</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="FF0070C0"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Hanns Zischler</t>
+          </r>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr"/>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>Hanns Zischler: Munich</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>汉斯·齐施勒: 慕尼黑</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>12:00 PM Q&amp;A: Paweł Pawlikowski, Hanns Zischler
 2:45 PM Q&amp;A: Paweł Pawlikowski, Hanns Zischler</t>
@@ -1069,26 +1239,27 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>LA GRADIVA</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Marine Atlan</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Marine Atlan</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="6" t="inlineStr"/>
-      <c r="G16" s="6" t="inlineStr"/>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="D16" s="6" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr"/>
+      <c r="F16" s="7" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr"/>
+      <c r="H16" s="8" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>5:45 PM Q&amp;A: Marine Atlan
 2:30 PM Q&amp;A: Marine Atlan</t>
@@ -1096,26 +1267,27 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>I DESERVE A LOVER WHOSE EVERY RISE SETS FIERY DOOMS RAGING ACROSS THE SKIES</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Mani Haghighi</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Mani Haghighi</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="6" t="inlineStr"/>
-      <c r="G17" s="6" t="inlineStr"/>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="D17" s="6" t="inlineStr"/>
+      <c r="E17" s="6" t="inlineStr"/>
+      <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="8" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>6:15 PM Q&amp;A: Mani Haghighi
 9:00 PM Q&amp;A: Mani Haghighi</t>
@@ -1123,26 +1295,27 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>I RARELY WAKE UP DREAMING</t>
         </is>
       </c>
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Isabelle Stever</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Isabelle Stever; Anna Melikova; Tania Myronyshena</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="6" t="inlineStr"/>
-      <c r="G18" s="6" t="inlineStr"/>
-      <c r="H18" s="4" t="inlineStr">
+      <c r="D18" s="6" t="inlineStr"/>
+      <c r="E18" s="6" t="inlineStr"/>
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="8" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>6:15 PM Q&amp;A: Isabelle Stever, Anna Melikova, Tania Myronyshena
 1:15 PM Q&amp;A: Isabelle Stever, Anna Melikova, Tania Myronyshena</t>
@@ -1150,26 +1323,27 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>THE LONELIEST MAN IN TOWN</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Tizza Covi and Rainer Frimmel</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Tizza Covi; Rainer Frimmel</t>
         </is>
       </c>
-      <c r="D19" s="5" t="inlineStr"/>
-      <c r="E19" s="5" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="D19" s="6" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr"/>
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>9:15 PM Q&amp;A: Tizza Covi, Rainer Frimmel
 12:30 PM Q&amp;A: Tizza Covi, Rainer Frimmel</t>
@@ -1177,17 +1351,17 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>A LONG WINTER</t>
         </is>
       </c>
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Andrew Haigh</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1221,6 +1395,7 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="FF0070C0"/>
               <sz val="11"/>
             </rPr>
             <t>Ebon Moss-Bachrach</t>
@@ -1235,6 +1410,7 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="FF0070C0"/>
               <sz val="11"/>
             </rPr>
             <t>Caitríona Balfe</t>
@@ -1249,6 +1425,7 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="FF0070C0"/>
               <sz val="11"/>
             </rPr>
             <t>Kit Connor</t>
@@ -1269,19 +1446,26 @@
           </r>
         </is>
       </c>
-      <c r="D20" s="5" t="inlineStr"/>
-      <c r="E20" s="5" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>Fred Hechinger: Gladiator II</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="inlineStr">
-        <is>
-          <t>Fred Hechinger: 神鬼戰士II</t>
-        </is>
-      </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="D20" s="6" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr"/>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Fred Hechinger: Gladiator II
+Ebon Moss-Bachrach: Mona Lisa Smile
+Caitríona Balfe: Now You See Me
+Kit Connor: Rocketman</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>弗雷德·海辛格: 神鬼戰士II
+艾邦·摩斯-貝克許: 蒙娜丽莎的微笑
+凯特瑞娜 · 巴菲: 惊天魔盗团
+基特·康納: 火箭人</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>9:15 PM Q&amp;A: Andrew Haigh, Fred Hechinger, Ebon Moss-Bachrach, Caitríona Balfe, Kit Connor, D'Pharaoh Woon-A-Tai
 3:15 PM Q&amp;A: Andrew Haigh, Fred Hechinger, Ebon Moss-Bachrach, Caitríona Balfe, Kit Connor, D'Pharaoh Woon-A-Tai</t>
@@ -1289,26 +1473,80 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>THE MAN I LOVE</t>
         </is>
       </c>
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Ira Sachs</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Ira Sachs; Rami Malek; Ebon Moss-Bachrach</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr"/>
-      <c r="E21" s="5" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Ira Sachs</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="FF008000"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Rami Malek</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="FF0070C0"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Ebon Moss-Bachrach</t>
+          </r>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Rami Malek: Oppenheimer, 24, Bohemian Rhapsody</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>拉米·马雷克: 奥本海默, 24小时（电视剧）, 波希米亞狂想曲</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Ebon Moss-Bachrach: Mona Lisa Smile</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>艾邦·摩斯-貝克許: 蒙娜丽莎的微笑</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>6:00 PM Q&amp;A: Ira Sachs, Rami Malek, Ebon Moss-Bachrach
 3:30 PM Q&amp;A: Ira Sachs, Rami Malek, Ebon Moss-Bachrach</t>
@@ -1316,26 +1554,27 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>A MAN OF HIS TIME</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Emmanuel Marre</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Emmanuel Marre</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="6" t="inlineStr"/>
-      <c r="G22" s="6" t="inlineStr"/>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="D22" s="6" t="inlineStr"/>
+      <c r="E22" s="6" t="inlineStr"/>
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="8" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>8:15 PM Q&amp;A: Emmanuel Marre
 2:30 PM Q&amp;A: Emmanuel Marre</t>
@@ -1343,26 +1582,43 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>MINOTAUR</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Andrey Zvyagintsev</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Andrey Zvyagintsev</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="6" t="inlineStr"/>
-      <c r="G23" s="6" t="inlineStr"/>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="FF008000"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Andrey Zvyagintsev</t>
+          </r>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Andrey Zvyagintsev: Leviathan, The Return, Loveless</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>安德烈·萨金塞夫: 利维坦, 回归, 无爱可诉</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="8" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>3:00 PM Q&amp;A: Andrey Zvyagintsev
 11:30 AM Q&amp;A: Andrey Zvyagintsev</t>
@@ -1370,46 +1626,18 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>MISTY GREEN</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Chris Rock</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Chris Rock</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">; </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="11"/>
-            </rPr>
-            <t>Rosalind Eleazar</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">; </t>
-          </r>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
           <r>
             <rPr>
               <rFont val="Calibri"/>
@@ -1417,7 +1645,21 @@
               <color rgb="FF008000"/>
               <sz val="11"/>
             </rPr>
-            <t>Daniel Kaluuya</t>
+            <t>Chris Rock</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Rosalind Eleazar</t>
           </r>
           <r>
             <rPr>
@@ -1433,6 +1675,22 @@
               <color rgb="FF008000"/>
               <sz val="11"/>
             </rPr>
+            <t>Daniel Kaluuya</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="FF008000"/>
+              <sz val="11"/>
+            </rPr>
             <t>Topher Grace</t>
           </r>
           <r>
@@ -1445,27 +1703,39 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="FF0070C0"/>
               <sz val="11"/>
             </rPr>
             <t>Amy Landecker</t>
           </r>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Daniel Kaluuya: Black Panther, Black Mirror, Black Panther: Wakanda Forever
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Chris Rock: A.I. Artificial Intelligence, Dogma, Grown Ups
+Daniel Kaluuya: Black Panther, Black Mirror, Get Out
 Topher Grace: Interstellar, Spider-Man 3, Ocean's Eleven</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>丹尼尔·卡卢亚: 黑豹, 黑镜, 黑豹2
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>克里斯·罗克: 人工智能, 怒犯天條, 亞當等大人
+丹尼尔·卡卢亚: 黑豹, 黑镜, 逃出绝命镇
 托弗·格雷斯: 星际穿越, 蜘蛛人3, 十一罗汉</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr"/>
-      <c r="G24" s="6" t="inlineStr"/>
-      <c r="H24" s="4" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Amy Landecker: House M.D.</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>愛咪·蘭德克: 豪斯医生</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>9:15 PM Q&amp;A: Chris Rock, Rosalind Eleazar, Daniel Kaluuya, Topher Grace, Amy Landecker
 11:30 AM Q&amp;A: Chris Rock, Rosalind Eleazar, Daniel Kaluuya, Topher Grace, Amy Landecker</t>
@@ -1473,52 +1743,69 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>MY UNDESIRABLE FRIENDS: PART II – EXILE</t>
         </is>
       </c>
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Julia Loktev</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Julia Loktev; Ksenia Mironova; Alesya Marokhovskaya; Irina Dolinina; Sonya Groysman; Elena Kostyuchenko</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr"/>
-      <c r="E25" s="5" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr"/>
+      <c r="E25" s="6" t="inlineStr"/>
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="8" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>11:45 AM Q&amp;A: Julia Loktev, Ksenia Mironova, Alesya Marokhovskaya, Irina Dolinina, Sonya Groysman, Elena Kostyuchenko</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>MY WIFE CRIES</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Angela Schanelec</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Angela Schanelec</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr"/>
-      <c r="E26" s="5" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="FF0070C0"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Angela Schanelec</t>
+          </r>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr"/>
+      <c r="E26" s="6" t="inlineStr"/>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Angela Schanelec: I Was at Home, But …</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>安姬拉·夏娜莱克: 我當時在家，但...</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>9:30 PM Q&amp;A: Angela Schanelec
 6:15 PM Q&amp;A: Angela Schanelec</t>
@@ -1526,26 +1813,27 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>ONCE UPON A TIME IN HARLEM</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>William Greaves and David Greaves</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>David Greaves; Liani Greaves; Anne de Mare</t>
         </is>
       </c>
-      <c r="D27" s="5" t="inlineStr"/>
-      <c r="E27" s="5" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="D27" s="6" t="inlineStr"/>
+      <c r="E27" s="6" t="inlineStr"/>
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="8" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>8:30 PM Q&amp;A: David Greaves, Liani Greaves, Anne de Mare
 6:15 PM Q&amp;A: David Greaves, Liani Greaves, Anne de Mare</t>
@@ -1553,17 +1841,17 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>POSSIBLE LOVE</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Lee Chang-dong</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1611,6 +1899,7 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="FF0070C0"/>
               <sz val="11"/>
             </rPr>
             <t>Zo In-sung</t>
@@ -1625,25 +1914,31 @@
           <r>
             <rPr>
               <rFont val="Calibri"/>
+              <color rgb="FF0070C0"/>
               <sz val="11"/>
             </rPr>
             <t>Cho Yeo-jeong</t>
           </r>
         </is>
       </c>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>Jeon Do-yeon: Ashfall</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>Jeon Do-yeon: 白头山</t>
-        </is>
-      </c>
-      <c r="H28" s="4" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr"/>
+      <c r="E28" s="6" t="inlineStr"/>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>Jeon Do-yeon: Ashfall
+Zo In-sung: Hope
+Cho Yeo-jeong: Parasite</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>全度妍: 白头山
+赵寅成: Hope
+曹汝贞: 寄生虫</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>5:30 PM Q&amp;A: Lee Chang-dong, Jeon Do-yeon, Sul Kyung-gu, Zo In-sung, Cho Yeo-jeong
 11:30 AM Q&amp;A: Lee Chang-dong</t>
@@ -1651,26 +1946,57 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>ROSE</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Markus Schleinzer</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Markus Schleinzer; Sandra Hüller</t>
-        </is>
-      </c>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="6" t="inlineStr"/>
-      <c r="G29" s="6" t="inlineStr"/>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Markus Schleinzer</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="FF008000"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Sandra Hüller</t>
+          </r>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Sandra Hüller: Project Hail Mary, Anatomy of a Fall, The Zone of Interest</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>桑德拉·惠勒: 挽救计划, 坠落的审判, 利益区域</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="8" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>1:00 PM Q&amp;A: Markus Schleinzer, Sandra Hüller
 9:15 PM Q&amp;A: Markus Schleinzer</t>
@@ -1678,21 +2004,23 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>TENDER LOVING CARE</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Mike Leigh</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="FF008000"/>
               <sz val="11"/>
             </rPr>
             <t>Mike Leigh</t>
@@ -1728,19 +2056,28 @@
           </r>
         </is>
       </c>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>Mike Leigh: Secrets &amp; Lies, Vera Drake, Mr. Turner</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>麦克·李: 秘密與謊言, 天使薇拉卓克, 特纳先生</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>Marion Bailey: The Crown</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G30" s="7" t="inlineStr">
         <is>
           <t>馬里恩·貝利: 王冠</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr">
+      <c r="H30" s="8" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>6:00 PM Q&amp;A: Mike Leigh, Marion Bailey, Kate O'Flynn
 6:00 PM Q&amp;A: Mike Leigh, Marion Bailey, Kate O'Flynn</t>
@@ -1748,17 +2085,17 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>THE UNKNOWN</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Arthur Harari</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1784,19 +2121,20 @@
           </r>
         </is>
       </c>
-      <c r="D31" s="5" t="inlineStr"/>
-      <c r="E31" s="5" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr">
-        <is>
-          <t>Niels Schneider: Heartbeats</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>尼尔斯·施内德: 心跳</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="inlineStr">
+      <c r="D31" s="6" t="inlineStr"/>
+      <c r="E31" s="6" t="inlineStr"/>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Niels Schneider: I Killed My Mother</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>尼尔斯·施内德: 殺死我阿媽</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>8:45 PM Q&amp;A: Arthur Harari, Niels Schneider
 12:45 PM Q&amp;A: Arthur Harari, Niels Schneider</t>
@@ -1804,26 +2142,70 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>GODZILLA MINUS ZERO</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Takashi Yamazaki</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Takashi Yamazaki; Ryunosuke Kamiki; Minami Hamabe</t>
-        </is>
-      </c>
-      <c r="D32" s="5" t="inlineStr"/>
-      <c r="E32" s="5" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="4" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Takashi Yamazaki</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Ryunosuke Kamiki</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="FF0070C0"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Minami Hamabe</t>
+          </r>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr"/>
+      <c r="E32" s="6" t="inlineStr"/>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>Minami Hamabe: Godzilla Minus One</t>
+        </is>
+      </c>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>滨边美波: 哥斯拉-1.0</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>6:00 PM Q&amp;A: Takashi Yamazaki, Ryunosuke Kamiki, Minami Hamabe
 2:15 PM Q&amp;A: Takashi Yamazaki</t>
@@ -1831,52 +2213,54 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>CAMERON WINTER AT CARNEGIE HALL</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Paul Thomas Anderson</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Paul Thomas Anderson; Cameron Winter</t>
         </is>
       </c>
-      <c r="D33" s="5" t="inlineStr"/>
-      <c r="E33" s="5" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr"/>
+      <c r="E33" s="6" t="inlineStr"/>
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>9:15 PM INTRO: Paul Thomas Anderson, Cameron Winter</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>CLUB KID</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Jordan Firstman</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Jordan Firstman</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr"/>
-      <c r="E34" s="5" t="inlineStr"/>
-      <c r="F34" s="6" t="inlineStr"/>
-      <c r="G34" s="6" t="inlineStr"/>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr"/>
+      <c r="E34" s="6" t="inlineStr"/>
+      <c r="F34" s="7" t="inlineStr"/>
+      <c r="G34" s="7" t="inlineStr"/>
+      <c r="H34" s="8" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>9:15 PM Q&amp;A: Jordan Firstman
 2:45 PM Q&amp;A: Jordan Firstman</t>
@@ -1884,26 +2268,79 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>THE DEBUT</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Jesse Eisenberg</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Jesse Eisenberg; Julianne Moore; Paul Giamatti</t>
-        </is>
-      </c>
-      <c r="D35" s="5" t="inlineStr"/>
-      <c r="E35" s="5" t="inlineStr"/>
-      <c r="F35" s="6" t="inlineStr"/>
-      <c r="G35" s="6" t="inlineStr"/>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="FF008000"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Jesse Eisenberg</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="FF008000"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Julianne Moore</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="FF008000"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Paul Giamatti</t>
+          </r>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>Jesse Eisenberg: The Social Network, Batman v Superman: Dawn of Justice, Justice League
+Julianne Moore: The Lost World: Jurassic Park, The Big Lebowski, The Hours
+Paul Giamatti: Saving Private Ryan, 12 Years a Slave, The Truman Show</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>杰西·艾森伯格: 社交网络, 蝙蝠俠對超人：正義曙光, 正義聯盟 I
+朱丽安·摩尔: 侏罗纪公园：失落的世界, 谋杀绿脚趾, 时时刻刻
+保罗·吉亚玛提: 拯救大兵瑞恩, 为奴十二年, 楚门的世界</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr"/>
+      <c r="G35" s="7" t="inlineStr"/>
+      <c r="H35" s="8" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>8:30 PM Q&amp;A: Jesse Eisenberg, Julianne Moore, Paul Giamatti
 3:15 PM Q&amp;A</t>
@@ -1911,26 +2348,27 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>EDWARD SAID: BETWEEN WORLDS</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Maiken Baird</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Maiken Baird</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr"/>
-      <c r="E36" s="5" t="inlineStr"/>
-      <c r="F36" s="6" t="inlineStr"/>
-      <c r="G36" s="6" t="inlineStr"/>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr"/>
+      <c r="E36" s="6" t="inlineStr"/>
+      <c r="F36" s="7" t="inlineStr"/>
+      <c r="G36" s="7" t="inlineStr"/>
+      <c r="H36" s="8" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>8:45 PM Q&amp;A: Maiken Baird
 6:15 PM Q&amp;A: Maiken Baird</t>
@@ -1938,17 +2376,17 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>FJORD</t>
         </is>
       </c>
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Cristian Mungiu</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1975,19 +2413,20 @@
           </r>
         </is>
       </c>
-      <c r="D37" s="5" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>Sebastian Stan: Avengers: Endgame, Avengers: Infinity War, Captain America: The First Avenger</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>塞巴斯蒂安·斯坦: 复仇者联盟4, 复仇者联盟3：无限战争, 美国队长</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr"/>
-      <c r="G37" s="6" t="inlineStr"/>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="7" t="inlineStr"/>
+      <c r="H37" s="8" t="inlineStr"/>
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>8:45 PM Q&amp;A: Cristian Mungiu, Sebastian Stan
 5:00 PM Q&amp;A: Cristian Mungiu, Sebastian Stan</t>
@@ -1995,26 +2434,27 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>IRON BOY</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Louis Clichy</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Chloe Aubert; Céline Vanlint</t>
         </is>
       </c>
-      <c r="D38" s="5" t="inlineStr"/>
-      <c r="E38" s="5" t="inlineStr"/>
-      <c r="F38" s="6" t="inlineStr"/>
-      <c r="G38" s="6" t="inlineStr"/>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr"/>
+      <c r="E38" s="6" t="inlineStr"/>
+      <c r="F38" s="7" t="inlineStr"/>
+      <c r="G38" s="7" t="inlineStr"/>
+      <c r="H38" s="8" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>10:30 AM Q&amp;A: Chloe Aubert, Céline Vanlint
 12:00 PM Q&amp;A: Chloe Aubert, Céline Vanlint</t>
@@ -2022,52 +2462,70 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>JOY OF JOYS</t>
         </is>
       </c>
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Jonathan Glazer</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Jonathan Glazer; Mica Levi; Rich Clarke</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr"/>
-      <c r="E39" s="5" t="inlineStr"/>
-      <c r="F39" s="6" t="inlineStr"/>
-      <c r="G39" s="6" t="inlineStr"/>
-      <c r="H39" s="4" t="inlineStr">
+      <c r="D39" s="6" t="inlineStr"/>
+      <c r="E39" s="6" t="inlineStr"/>
+      <c r="F39" s="7" t="inlineStr"/>
+      <c r="G39" s="7" t="inlineStr"/>
+      <c r="H39" s="8" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr">
         <is>
           <t>6:00 PM Q&amp;A: Jonathan Glazer, Mica Levi, Rich Clarke</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>MAKING MARIE ANTOINETTE</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Eleanor Coppola</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>Sofia Coppola</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr"/>
-      <c r="E40" s="5" t="inlineStr"/>
-      <c r="F40" s="6" t="inlineStr"/>
-      <c r="G40" s="6" t="inlineStr"/>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="FF008000"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Sofia Coppola</t>
+          </r>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>Sofia Coppola: The Godfather, Star Wars: Episode I – The Phantom Menace, The Godfather Part II</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>索菲亚·科波拉: 教父, 星球大战I：幽灵的威胁, 教父2</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr"/>
+      <c r="G40" s="7" t="inlineStr"/>
+      <c r="H40" s="8" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>6:00 PM Q&amp;A: Sofia Coppola
 3:45 PM Q&amp;A: Sofia Coppola</t>
@@ -2075,26 +2533,87 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>ONE MORE TIME</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Cindy Kleine and André Gregory</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>André Gregory; Cindy Kleine; Larry Pine; Gerry Bamman</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr"/>
-      <c r="E41" s="5" t="inlineStr"/>
-      <c r="F41" s="6" t="inlineStr"/>
-      <c r="G41" s="6" t="inlineStr"/>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="FF0070C0"/>
+              <sz val="11"/>
+            </rPr>
+            <t>André Gregory</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Cindy Kleine</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Larry Pine</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="FF0070C0"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Gerry Bamman</t>
+          </r>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr"/>
+      <c r="E41" s="6" t="inlineStr"/>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>André Gregory: Demolition Man
+Gerry Bamman: Home Alone</t>
+        </is>
+      </c>
+      <c r="G41" s="7" t="inlineStr">
+        <is>
+          <t>安德烈·古格里: 越空狂龍
+Gerry Bamman: 小鬼当家</t>
+        </is>
+      </c>
+      <c r="H41" s="8" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>4:00 PM Q&amp;A: André Gregory, Cindy Kleine, Larry Pine, Gerry Bamman
 6:30 PM Q&amp;A: André Gregory, Cindy Kleine, Larry Pine, Gerry Bamman</t>
@@ -2102,38 +2621,25 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>THE ONLY LIVING PICKPOCKET IN NEW YORK</t>
         </is>
       </c>
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Noah Segan</t>
         </is>
       </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="FF0070C0"/>
               <sz val="11"/>
             </rPr>
             <t>Noah Segan</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="11"/>
-            </rPr>
-            <t xml:space="preserve">; </t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="Calibri"/>
-              <sz val="11"/>
-            </rPr>
-            <t>John Turturro</t>
           </r>
           <r>
             <rPr>
@@ -2149,49 +2655,77 @@
               <color rgb="FF008000"/>
               <sz val="11"/>
             </rPr>
+            <t>John Turturro</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">; </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <b val="1"/>
+              <color rgb="FF008000"/>
+              <sz val="11"/>
+            </rPr>
             <t>Tatiana Maslany</t>
           </r>
         </is>
       </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>Tatiana Maslany: She-Hulk: Attorney at Law, Eastern Promises, The Vow</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>塔提阿娜·玛斯拉尼: 女浩克, 东方的承诺, 誓約</t>
-        </is>
-      </c>
-      <c r="F42" s="6" t="inlineStr"/>
-      <c r="G42" s="6" t="inlineStr"/>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>John Turturro: Transformers, The Batman, Transformers: Dark of the Moon
+Tatiana Maslany: She-Hulk: Attorney at Law, Eastern Promises, The Vow</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>约翰·图尔特罗: 变形金刚, 蝙蝠侠, 变形金刚3
+塔提阿娜·玛斯拉尼: 女浩克, 东方的承诺, 誓約</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>Noah Segan: Looper</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>諾亞·塞根: 迴路殺手</t>
+        </is>
+      </c>
+      <c r="H42" s="8" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>6:00 PM Q&amp;A: Noah Segan, John Turturro, Tatiana Maslany</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>SIXTEEN MOMENTS OF MY LIFE</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Albert Serra</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>Albert Serra</t>
         </is>
       </c>
-      <c r="D43" s="5" t="inlineStr"/>
-      <c r="E43" s="5" t="inlineStr"/>
-      <c r="F43" s="6" t="inlineStr"/>
-      <c r="G43" s="6" t="inlineStr"/>
-      <c r="H43" s="4" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr"/>
+      <c r="E43" s="6" t="inlineStr"/>
+      <c r="F43" s="7" t="inlineStr"/>
+      <c r="G43" s="7" t="inlineStr"/>
+      <c r="H43" s="8" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>6:30 PM Q&amp;A: Albert Serra
 1:00 PM Q&amp;A: Albert Serra</t>
@@ -2199,17 +2733,17 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>A STATEMENT</t>
         </is>
       </c>
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Tom McCarthy</t>
         </is>
       </c>
-      <c r="C44" s="4" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2221,71 +2755,74 @@
           </r>
         </is>
       </c>
-      <c r="D44" s="5" t="inlineStr"/>
-      <c r="E44" s="5" t="inlineStr"/>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="D44" s="6" t="inlineStr"/>
+      <c r="E44" s="6" t="inlineStr"/>
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>Tom McCarthy: 2012</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr">
+      <c r="G44" s="7" t="inlineStr">
         <is>
           <t>湯瑪士·麥卡錫: 2012</t>
         </is>
       </c>
-      <c r="H44" s="4" t="inlineStr">
+      <c r="H44" s="8" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>6:15 PM Q&amp;A: Tom McCarthy</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>YOU CAN SEE EVERYTHING</t>
         </is>
       </c>
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>Nathan Fielder and Lance Oppenheim</t>
         </is>
       </c>
-      <c r="C45" s="4" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>Nathan Fielder; Lance Oppenheim</t>
         </is>
       </c>
-      <c r="D45" s="5" t="inlineStr"/>
-      <c r="E45" s="5" t="inlineStr"/>
-      <c r="F45" s="6" t="inlineStr"/>
-      <c r="G45" s="6" t="inlineStr"/>
-      <c r="H45" s="4" t="inlineStr">
+      <c r="D45" s="6" t="inlineStr"/>
+      <c r="E45" s="6" t="inlineStr"/>
+      <c r="F45" s="7" t="inlineStr"/>
+      <c r="G45" s="7" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr"/>
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>8:00 PM Q&amp;A: Nathan Fielder, Lance Oppenheim</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>SPOTLIGHT SHORTS</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>Kleber Mendonça Filho, Kamal Aljafari, Camilo Restrepo, Jia Zhangke, Morgan Fisher</t>
         </is>
       </c>
-      <c r="C46" s="4" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Kamal Aljafari; Camilo Restrepo</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr"/>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="6" t="inlineStr"/>
-      <c r="G46" s="6" t="inlineStr"/>
-      <c r="H46" s="4" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr"/>
+      <c r="E46" s="6" t="inlineStr"/>
+      <c r="F46" s="7" t="inlineStr"/>
+      <c r="G46" s="7" t="inlineStr"/>
+      <c r="H46" s="8" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr">
         <is>
           <t>6:30 PM Q&amp;A: Kamal Aljafari, Camilo Restrepo
 9:00 PM Q&amp;A: Kamal Aljafari, Camilo Restrepo</t>
@@ -2293,26 +2830,27 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>NEW YORK SHORTS</t>
         </is>
       </c>
-      <c r="B47" s="4" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>J. Wortham, Heather Landsman, Eliza Barry Callahan, Fanny Texier, Charlotte Wells</t>
         </is>
       </c>
-      <c r="C47" s="4" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>J. Wortham; Heather Landsman; Eliza Barry Callahan; Fanny Texier; Charlotte Wells</t>
         </is>
       </c>
-      <c r="D47" s="5" t="inlineStr"/>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="6" t="inlineStr"/>
-      <c r="G47" s="6" t="inlineStr"/>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr"/>
+      <c r="E47" s="6" t="inlineStr"/>
+      <c r="F47" s="7" t="inlineStr"/>
+      <c r="G47" s="7" t="inlineStr"/>
+      <c r="H47" s="8" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>9:15 PM Q&amp;A: J. Wortham, Heather Landsman, Eliza Barry Callahan, Fanny Texier, Charlotte Wells
 12:45 PM Q&amp;A: J. Wortham, Heather Landsman, Eliza Barry Callahan, Fanny Texier, Charlotte Wells</t>
@@ -2320,26 +2858,27 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>BARDI</t>
         </is>
       </c>
-      <c r="B48" s="4" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Tala Hadid</t>
         </is>
       </c>
-      <c r="C48" s="4" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Tala Hadid</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr"/>
-      <c r="E48" s="5" t="inlineStr"/>
-      <c r="F48" s="6" t="inlineStr"/>
-      <c r="G48" s="6" t="inlineStr"/>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr"/>
+      <c r="E48" s="6" t="inlineStr"/>
+      <c r="F48" s="7" t="inlineStr"/>
+      <c r="G48" s="7" t="inlineStr"/>
+      <c r="H48" s="8" t="inlineStr"/>
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>6:15 PM Q&amp;A: Tala Hadid
 9:15 PM Q&amp;A: Tala Hadid</t>
@@ -2347,26 +2886,27 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>AT NIGHT</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>Beatrice Gibson</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>Beatrice Gibson</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr"/>
-      <c r="E49" s="5" t="inlineStr"/>
-      <c r="F49" s="6" t="inlineStr"/>
-      <c r="G49" s="6" t="inlineStr"/>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr"/>
+      <c r="E49" s="6" t="inlineStr"/>
+      <c r="F49" s="7" t="inlineStr"/>
+      <c r="G49" s="7" t="inlineStr"/>
+      <c r="H49" s="8" t="inlineStr"/>
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>9:00 PM Q&amp;A: Beatrice Gibson
 5:30 PM Q&amp;A: Beatrice Gibson</t>
@@ -2374,26 +2914,27 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>A DAY IN THE LIFE OF JO: CHAPTER PHAEDRA</t>
         </is>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>Jacqueline Lentzou</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>Jacqueline Lentzou</t>
         </is>
       </c>
-      <c r="D50" s="5" t="inlineStr"/>
-      <c r="E50" s="5" t="inlineStr"/>
-      <c r="F50" s="6" t="inlineStr"/>
-      <c r="G50" s="6" t="inlineStr"/>
-      <c r="H50" s="4" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr"/>
+      <c r="E50" s="6" t="inlineStr"/>
+      <c r="F50" s="7" t="inlineStr"/>
+      <c r="G50" s="7" t="inlineStr"/>
+      <c r="H50" s="8" t="inlineStr"/>
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>3:30 PM Q&amp;A: Jacqueline Lentzou
 6:45 PM Q&amp;A: Jacqueline Lentzou</t>
@@ -2401,26 +2942,27 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>FOR THE MOON</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>Éric Baudelaire</t>
         </is>
       </c>
-      <c r="C51" s="4" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Baudelaire; Claire Atherton</t>
         </is>
       </c>
-      <c r="D51" s="5" t="inlineStr"/>
-      <c r="E51" s="5" t="inlineStr"/>
-      <c r="F51" s="6" t="inlineStr"/>
-      <c r="G51" s="6" t="inlineStr"/>
-      <c r="H51" s="4" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr"/>
+      <c r="E51" s="6" t="inlineStr"/>
+      <c r="F51" s="7" t="inlineStr"/>
+      <c r="G51" s="7" t="inlineStr"/>
+      <c r="H51" s="8" t="inlineStr"/>
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>9:00 PM Q&amp;A: Baudelaire, Claire Atherton
 6:15 PM Q&amp;A: Baudelaire, Claire Atherton</t>
@@ -2428,26 +2970,27 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>FOREIGN TRAVEL</t>
         </is>
       </c>
-      <c r="B52" s="4" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>Ted Fendt</t>
         </is>
       </c>
-      <c r="C52" s="4" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>Ted Fendt</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr"/>
-      <c r="E52" s="5" t="inlineStr"/>
-      <c r="F52" s="6" t="inlineStr"/>
-      <c r="G52" s="6" t="inlineStr"/>
-      <c r="H52" s="4" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr"/>
+      <c r="E52" s="6" t="inlineStr"/>
+      <c r="F52" s="7" t="inlineStr"/>
+      <c r="G52" s="7" t="inlineStr"/>
+      <c r="H52" s="8" t="inlineStr"/>
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>9:15 PM Q&amp;A: Ted Fendt
 6:45 PM Q&amp;A: Ted Fendt</t>
@@ -2455,26 +2998,27 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>HANABI</t>
         </is>
       </c>
-      <c r="B53" s="4" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>Ana Vaz</t>
         </is>
       </c>
-      <c r="C53" s="4" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>Ana Vaz</t>
         </is>
       </c>
-      <c r="D53" s="5" t="inlineStr"/>
-      <c r="E53" s="5" t="inlineStr"/>
-      <c r="F53" s="6" t="inlineStr"/>
-      <c r="G53" s="6" t="inlineStr"/>
-      <c r="H53" s="4" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr"/>
+      <c r="E53" s="6" t="inlineStr"/>
+      <c r="F53" s="7" t="inlineStr"/>
+      <c r="G53" s="7" t="inlineStr"/>
+      <c r="H53" s="8" t="inlineStr"/>
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>8:45 PM Q&amp;A: Ana Vaz
 6:15 PM Q&amp;A: Ana Vaz</t>
@@ -2482,26 +3026,42 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>HEIL JUPITER!</t>
         </is>
       </c>
-      <c r="B54" s="4" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>Carlos Reygadas</t>
         </is>
       </c>
-      <c r="C54" s="4" t="inlineStr">
-        <is>
-          <t>Carlos Reygadas</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr"/>
-      <c r="E54" s="5" t="inlineStr"/>
-      <c r="F54" s="6" t="inlineStr"/>
-      <c r="G54" s="6" t="inlineStr"/>
-      <c r="H54" s="4" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri"/>
+              <color rgb="FF0070C0"/>
+              <sz val="11"/>
+            </rPr>
+            <t>Carlos Reygadas</t>
+          </r>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr"/>
+      <c r="E54" s="6" t="inlineStr"/>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>Carlos Reygadas: Silent Light</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>卡洛斯·雷加达斯: 寂靜之光</t>
+        </is>
+      </c>
+      <c r="H54" s="8" t="inlineStr"/>
+      <c r="I54" s="5" t="inlineStr">
         <is>
           <t>2:15 PM Q&amp;A: Carlos Reygadas
 6:00 PM Q&amp;A: Carlos Reygadas</t>
@@ -2509,26 +3069,27 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>LIFE OF JORGE LUIS BORGES</t>
         </is>
       </c>
-      <c r="B55" s="4" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>Mariano Llinás</t>
         </is>
       </c>
-      <c r="C55" s="4" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>Mariano Llinás</t>
         </is>
       </c>
-      <c r="D55" s="5" t="inlineStr"/>
-      <c r="E55" s="5" t="inlineStr"/>
-      <c r="F55" s="6" t="inlineStr"/>
-      <c r="G55" s="6" t="inlineStr"/>
-      <c r="H55" s="4" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr"/>
+      <c r="E55" s="6" t="inlineStr"/>
+      <c r="F55" s="7" t="inlineStr"/>
+      <c r="G55" s="7" t="inlineStr"/>
+      <c r="H55" s="8" t="inlineStr"/>
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>5:15 PM Q&amp;A: Mariano Llinás
 12:00 PM Q&amp;A: Mariano Llinás</t>
@@ -2536,26 +3097,27 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>LONDON</t>
         </is>
       </c>
-      <c r="B56" s="4" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>Sebastian Brameshuber</t>
         </is>
       </c>
-      <c r="C56" s="4" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>Sebastian Brameshuber; Bobby Sommer</t>
         </is>
       </c>
-      <c r="D56" s="5" t="inlineStr"/>
-      <c r="E56" s="5" t="inlineStr"/>
-      <c r="F56" s="6" t="inlineStr"/>
-      <c r="G56" s="6" t="inlineStr"/>
-      <c r="H56" s="4" t="inlineStr">
+      <c r="D56" s="6" t="inlineStr"/>
+      <c r="E56" s="6" t="inlineStr"/>
+      <c r="F56" s="7" t="inlineStr"/>
+      <c r="G56" s="7" t="inlineStr"/>
+      <c r="H56" s="8" t="inlineStr"/>
+      <c r="I56" s="5" t="inlineStr">
         <is>
           <t>6:00 PM Q&amp;A: Sebastian Brameshuber, Bobby Sommer
 9:15 PM Q&amp;A: Sebastian Brameshuber, Bobby Sommer</t>
@@ -2563,26 +3125,27 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>OVERT LISTENING</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B57" s="5" t="inlineStr">
         <is>
           <t>Tiffany Sia</t>
         </is>
       </c>
-      <c r="C57" s="4" t="inlineStr">
+      <c r="C57" s="5" t="inlineStr">
         <is>
           <t>Tiffany Sia</t>
         </is>
       </c>
-      <c r="D57" s="5" t="inlineStr"/>
-      <c r="E57" s="5" t="inlineStr"/>
-      <c r="F57" s="6" t="inlineStr"/>
-      <c r="G57" s="6" t="inlineStr"/>
-      <c r="H57" s="4" t="inlineStr">
+      <c r="D57" s="6" t="inlineStr"/>
+      <c r="E57" s="6" t="inlineStr"/>
+      <c r="F57" s="7" t="inlineStr"/>
+      <c r="G57" s="7" t="inlineStr"/>
+      <c r="H57" s="8" t="inlineStr"/>
+      <c r="I57" s="5" t="inlineStr">
         <is>
           <t>12:00 PM Q&amp;A: Tiffany Sia
 2:45 PM Q&amp;A: Tiffany Sia</t>
@@ -2590,26 +3153,27 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>THE REMOTES</t>
         </is>
       </c>
-      <c r="B58" s="4" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>John Torres</t>
         </is>
       </c>
-      <c r="C58" s="4" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>John Torres</t>
         </is>
       </c>
-      <c r="D58" s="5" t="inlineStr"/>
-      <c r="E58" s="5" t="inlineStr"/>
-      <c r="F58" s="6" t="inlineStr"/>
-      <c r="G58" s="6" t="inlineStr"/>
-      <c r="H58" s="4" t="inlineStr">
+      <c r="D58" s="6" t="inlineStr"/>
+      <c r="E58" s="6" t="inlineStr"/>
+      <c r="F58" s="7" t="inlineStr"/>
+      <c r="G58" s="7" t="inlineStr"/>
+      <c r="H58" s="8" t="inlineStr"/>
+      <c r="I58" s="5" t="inlineStr">
         <is>
           <t>8:45 PM Q&amp;A: John Torres
 4:15 PM Q&amp;A: John Torres</t>
@@ -2617,26 +3181,27 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>SUICIDE NOTE</t>
         </is>
       </c>
-      <c r="B59" s="4" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>Fred Camper</t>
         </is>
       </c>
-      <c r="C59" s="4" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>Fred Camper; Kyle Westphal</t>
         </is>
       </c>
-      <c r="D59" s="5" t="inlineStr"/>
-      <c r="E59" s="5" t="inlineStr"/>
-      <c r="F59" s="6" t="inlineStr"/>
-      <c r="G59" s="6" t="inlineStr"/>
-      <c r="H59" s="4" t="inlineStr">
+      <c r="D59" s="6" t="inlineStr"/>
+      <c r="E59" s="6" t="inlineStr"/>
+      <c r="F59" s="7" t="inlineStr"/>
+      <c r="G59" s="7" t="inlineStr"/>
+      <c r="H59" s="8" t="inlineStr"/>
+      <c r="I59" s="5" t="inlineStr">
         <is>
           <t>6:00 PM Q&amp;A: Fred Camper, Kyle Westphal
 8:15 PM Q&amp;A: Fred Camper, Kyle Westphal</t>
@@ -2644,26 +3209,27 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>TOMORROW A LONG TIME AGO</t>
         </is>
       </c>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>Luise Donschen</t>
         </is>
       </c>
-      <c r="C60" s="4" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>Luise Donschen</t>
         </is>
       </c>
-      <c r="D60" s="5" t="inlineStr"/>
-      <c r="E60" s="5" t="inlineStr"/>
-      <c r="F60" s="6" t="inlineStr"/>
-      <c r="G60" s="6" t="inlineStr"/>
-      <c r="H60" s="4" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr"/>
+      <c r="E60" s="6" t="inlineStr"/>
+      <c r="F60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="8" t="inlineStr"/>
+      <c r="I60" s="5" t="inlineStr">
         <is>
           <t>6:15 PM Q&amp;A: Luise Donschen
 1:45 PM Q&amp;A: Luise Donschen</t>
@@ -2671,26 +3237,27 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>WHAT CAN’T BE MENTIONED</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>Dan Sallitt</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>Dan Sallitt; Tallie Medel; Sky Hirschkron; Kit Zauhar; Kyle McCormack</t>
         </is>
       </c>
-      <c r="D61" s="5" t="inlineStr"/>
-      <c r="E61" s="5" t="inlineStr"/>
-      <c r="F61" s="6" t="inlineStr"/>
-      <c r="G61" s="6" t="inlineStr"/>
-      <c r="H61" s="4" t="inlineStr">
+      <c r="D61" s="6" t="inlineStr"/>
+      <c r="E61" s="6" t="inlineStr"/>
+      <c r="F61" s="7" t="inlineStr"/>
+      <c r="G61" s="7" t="inlineStr"/>
+      <c r="H61" s="8" t="inlineStr"/>
+      <c r="I61" s="5" t="inlineStr">
         <is>
           <t>7:00 PM Q&amp;A: Dan Sallitt, Tallie Medel, Sky Hirschkron, Kit Zauhar, Kyle McCormack
 12:00 PM Q&amp;A: Dan Sallitt, Tallie Medel, Sky Hirschkron, Kit Zauhar, Kyle McCormack</t>
@@ -2698,26 +3265,27 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>CURRENTS PROGRAM 1: THE HIDDEN DIMENSION</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>Yixuan Zhang, Josh Weissbach, Natalia Marín, Jamie Crewe, Tatsu Aoki</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C62" s="5" t="inlineStr">
         <is>
           <t>Yixuan Zhang; Josh Weissbach; Ben Balcom; Natalia Marín; Jamie Crewe; Tatsu Aoki</t>
         </is>
       </c>
-      <c r="D62" s="5" t="inlineStr"/>
-      <c r="E62" s="5" t="inlineStr"/>
-      <c r="F62" s="6" t="inlineStr"/>
-      <c r="G62" s="6" t="inlineStr"/>
-      <c r="H62" s="4" t="inlineStr">
+      <c r="D62" s="6" t="inlineStr"/>
+      <c r="E62" s="6" t="inlineStr"/>
+      <c r="F62" s="7" t="inlineStr"/>
+      <c r="G62" s="7" t="inlineStr"/>
+      <c r="H62" s="8" t="inlineStr"/>
+      <c r="I62" s="5" t="inlineStr">
         <is>
           <t>12:15 PM Q&amp;A: Yixuan Zhang, Josh Weissbach, Ben Balcom, Natalia Marín, Jamie Crewe, Tatsu Aoki
 2:15 PM Q&amp;A: Yixuan Zhang, Josh Weissbach, Ben Balcom, Natalia Marín, Jamie Crewe, Tatsu Aoki</t>
@@ -2725,26 +3293,27 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>CURRENTS PROGRAM 2: THE VISIBLE INVISIBLE</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>James Richards, Artavazd Pelechian, Johann Lurf, Morgan Fisher</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>James Richards; Johann Lurf; Morgan Fisher</t>
         </is>
       </c>
-      <c r="D63" s="5" t="inlineStr"/>
-      <c r="E63" s="5" t="inlineStr"/>
-      <c r="F63" s="6" t="inlineStr"/>
-      <c r="G63" s="6" t="inlineStr"/>
-      <c r="H63" s="4" t="inlineStr">
+      <c r="D63" s="6" t="inlineStr"/>
+      <c r="E63" s="6" t="inlineStr"/>
+      <c r="F63" s="7" t="inlineStr"/>
+      <c r="G63" s="7" t="inlineStr"/>
+      <c r="H63" s="8" t="inlineStr"/>
+      <c r="I63" s="5" t="inlineStr">
         <is>
           <t>6:45 PM Q&amp;A: James Richards, Johann Lurf, Morgan Fisher
 12:15 PM Q&amp;A: James Richards, Johann Lurf</t>
@@ -2752,26 +3321,27 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="inlineStr">
+      <c r="A64" s="5" t="inlineStr">
         <is>
           <t>CURRENTS PROGRAM 3: SURFACE NOISE</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>Simon Liu, Jonathan Seungjoon Lee, Laura Kraning, Siegfried A. Fruhauf, Karissa Hahn, Cameron Worden</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>Simon Liu; Laura Kraning; Jonathan Seungjoon Lee; Karissa Hahn; Cameron Worden</t>
         </is>
       </c>
-      <c r="D64" s="5" t="inlineStr"/>
-      <c r="E64" s="5" t="inlineStr"/>
-      <c r="F64" s="6" t="inlineStr"/>
-      <c r="G64" s="6" t="inlineStr"/>
-      <c r="H64" s="4" t="inlineStr">
+      <c r="D64" s="6" t="inlineStr"/>
+      <c r="E64" s="6" t="inlineStr"/>
+      <c r="F64" s="7" t="inlineStr"/>
+      <c r="G64" s="7" t="inlineStr"/>
+      <c r="H64" s="8" t="inlineStr"/>
+      <c r="I64" s="5" t="inlineStr">
         <is>
           <t>9:00 PM Q&amp;A: Simon Liu, Laura Kraning, Jonathan Seungjoon Lee, Karissa Hahn, Cameron Worden
 7:00 PM Q&amp;A: Simon Liu, Laura Kraning, Jonathan Seungjoon Lee, Cameron Worden</t>
@@ -2779,26 +3349,27 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="A65" s="5" t="inlineStr">
         <is>
           <t>CURRENTS PROGRAM 4: THE REAL WORLD</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>Calum Walter, Martine Syms, Jesse McLean, Jiaqi Yu</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>Calum Walter; Martine Syms; Jesse McLean</t>
         </is>
       </c>
-      <c r="D65" s="5" t="inlineStr"/>
-      <c r="E65" s="5" t="inlineStr"/>
-      <c r="F65" s="6" t="inlineStr"/>
-      <c r="G65" s="6" t="inlineStr"/>
-      <c r="H65" s="4" t="inlineStr">
+      <c r="D65" s="6" t="inlineStr"/>
+      <c r="E65" s="6" t="inlineStr"/>
+      <c r="F65" s="7" t="inlineStr"/>
+      <c r="G65" s="7" t="inlineStr"/>
+      <c r="H65" s="8" t="inlineStr"/>
+      <c r="I65" s="5" t="inlineStr">
         <is>
           <t>7:15 PM Q&amp;A: Calum Walter, Martine Syms, Jesse McLean
 6:00 PM Q&amp;A: Calum Walter, Martine Syms, Jesse McLean</t>
@@ -2806,26 +3377,27 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="A66" s="5" t="inlineStr">
         <is>
           <t>CURRENTS PROGRAM 5: THE MATERIAL GHOST</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>Peggy Ahwesh, Kevin Jerome Everson, Adam Piron, Bani Khoshnoudi</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>Peggy Ahwesh; Adam Piron; Bani Khoshnoudi</t>
         </is>
       </c>
-      <c r="D66" s="5" t="inlineStr"/>
-      <c r="E66" s="5" t="inlineStr"/>
-      <c r="F66" s="6" t="inlineStr"/>
-      <c r="G66" s="6" t="inlineStr"/>
-      <c r="H66" s="4" t="inlineStr">
+      <c r="D66" s="6" t="inlineStr"/>
+      <c r="E66" s="6" t="inlineStr"/>
+      <c r="F66" s="7" t="inlineStr"/>
+      <c r="G66" s="7" t="inlineStr"/>
+      <c r="H66" s="8" t="inlineStr"/>
+      <c r="I66" s="5" t="inlineStr">
         <is>
           <t>9:30 PM Q&amp;A: Peggy Ahwesh, Adam Piron, Bani Khoshnoudi
 4:00 PM Q&amp;A: Peggy Ahwesh, Adam Piron, Bani Khoshnoudi</t>
@@ -2833,26 +3405,27 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+      <c r="A67" s="5" t="inlineStr">
         <is>
           <t>CURRENTS PROGRAM 6: OUT OF THE PRESENT</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>Laura Poitras, Rachel Lauren Mueller, Ben Russell, Vika Kirchenbauer, Mara Chavez, doris duhennois</t>
         </is>
       </c>
-      <c r="C67" s="4" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>Laura Poitras; Rachel Lauren Mueller; Ben Russell; Mara Chavez</t>
         </is>
       </c>
-      <c r="D67" s="5" t="inlineStr"/>
-      <c r="E67" s="5" t="inlineStr"/>
-      <c r="F67" s="6" t="inlineStr"/>
-      <c r="G67" s="6" t="inlineStr"/>
-      <c r="H67" s="4" t="inlineStr">
+      <c r="D67" s="6" t="inlineStr"/>
+      <c r="E67" s="6" t="inlineStr"/>
+      <c r="F67" s="7" t="inlineStr"/>
+      <c r="G67" s="7" t="inlineStr"/>
+      <c r="H67" s="8" t="inlineStr"/>
+      <c r="I67" s="5" t="inlineStr">
         <is>
           <t>8:45 PM Q&amp;A: Laura Poitras, Rachel Lauren Mueller, Ben Russell, Mara Chavez
 9:00 PM Q&amp;A: Laura Poitras, Rachel Lauren Mueller, Ben Russell, Mara Chavez</t>
@@ -2860,43 +3433,44 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="inlineStr">
+      <c r="A68" s="5" t="inlineStr">
         <is>
           <t>THE DEVILS</t>
         </is>
       </c>
-      <c r="B68" s="4" t="inlineStr">
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>Ken Russell</t>
         </is>
       </c>
-      <c r="C68" s="4" t="inlineStr">
+      <c r="C68" s="5" t="inlineStr">
         <is>
           <t>Mark Kermode</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr"/>
-      <c r="E68" s="5" t="inlineStr"/>
-      <c r="F68" s="6" t="inlineStr"/>
-      <c r="G68" s="6" t="inlineStr"/>
-      <c r="H68" s="4" t="inlineStr">
+      <c r="D68" s="6" t="inlineStr"/>
+      <c r="E68" s="6" t="inlineStr"/>
+      <c r="F68" s="7" t="inlineStr"/>
+      <c r="G68" s="7" t="inlineStr"/>
+      <c r="H68" s="8" t="inlineStr"/>
+      <c r="I68" s="5" t="inlineStr">
         <is>
           <t>9:00 PM Q&amp;A: Mark Kermode</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="inlineStr">
+      <c r="A69" s="5" t="inlineStr">
         <is>
           <t>GONE TO EARTH</t>
         </is>
       </c>
-      <c r="B69" s="4" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>Michael Powell and Emeric Pressburger</t>
         </is>
       </c>
-      <c r="C69" s="4" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2909,45 +3483,47 @@
           </r>
         </is>
       </c>
-      <c r="D69" s="5" t="inlineStr">
+      <c r="D69" s="6" t="inlineStr">
         <is>
           <t>Martin Scorsese: The Departed, Taxi Driver, Taxi Driver</t>
         </is>
       </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="E69" s="6" t="inlineStr">
         <is>
           <t>马丁·斯科塞斯: 无间道风云, 出租车司机, 出租车司机</t>
         </is>
       </c>
-      <c r="F69" s="6" t="inlineStr"/>
-      <c r="G69" s="6" t="inlineStr"/>
-      <c r="H69" s="4" t="inlineStr">
+      <c r="F69" s="7" t="inlineStr"/>
+      <c r="G69" s="7" t="inlineStr"/>
+      <c r="H69" s="8" t="inlineStr"/>
+      <c r="I69" s="5" t="inlineStr">
         <is>
           <t>4:00 PM Q&amp;A: Martin Scorsese</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="inlineStr">
+      <c r="A70" s="5" t="inlineStr">
         <is>
           <t>NITRATE KISSES</t>
         </is>
       </c>
-      <c r="B70" s="4" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>Barbara Hammer</t>
         </is>
       </c>
-      <c r="C70" s="4" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>Florrie Burke; Brydie O'Connor</t>
         </is>
       </c>
-      <c r="D70" s="5" t="inlineStr"/>
-      <c r="E70" s="5" t="inlineStr"/>
-      <c r="F70" s="6" t="inlineStr"/>
-      <c r="G70" s="6" t="inlineStr"/>
-      <c r="H70" s="4" t="inlineStr">
+      <c r="D70" s="6" t="inlineStr"/>
+      <c r="E70" s="6" t="inlineStr"/>
+      <c r="F70" s="7" t="inlineStr"/>
+      <c r="G70" s="7" t="inlineStr"/>
+      <c r="H70" s="8" t="inlineStr"/>
+      <c r="I70" s="5" t="inlineStr">
         <is>
           <t>2:30 PM INTRO: Florrie Burke, Brydie O'Connor
 7:00 PM INTRO: Florrie Burke, Brydie O'Connor</t>
@@ -2955,26 +3531,27 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="inlineStr">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>A WELL FOR THE THIRSTY</t>
         </is>
       </c>
-      <c r="B71" s="4" t="inlineStr">
+      <c r="B71" s="5" t="inlineStr">
         <is>
           <t>Yuri Ilyenko</t>
         </is>
       </c>
-      <c r="C71" s="4" t="inlineStr">
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>Daniel Bird</t>
         </is>
       </c>
-      <c r="D71" s="5" t="inlineStr"/>
-      <c r="E71" s="5" t="inlineStr"/>
-      <c r="F71" s="6" t="inlineStr"/>
-      <c r="G71" s="6" t="inlineStr"/>
-      <c r="H71" s="4" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr"/>
+      <c r="E71" s="6" t="inlineStr"/>
+      <c r="F71" s="7" t="inlineStr"/>
+      <c r="G71" s="7" t="inlineStr"/>
+      <c r="H71" s="8" t="inlineStr"/>
+      <c r="I71" s="5" t="inlineStr">
         <is>
           <t>6:30 PM INTRO: Daniel Bird
 12:45 PM INTRO: Daniel Bird</t>
@@ -2982,26 +3559,27 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+      <c r="A72" s="5" t="inlineStr">
         <is>
           <t>YESTERDAY GIRL</t>
         </is>
       </c>
-      <c r="B72" s="4" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>Alexander Kluge</t>
         </is>
       </c>
-      <c r="C72" s="4" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>Sophie Kluge</t>
         </is>
       </c>
-      <c r="D72" s="5" t="inlineStr"/>
-      <c r="E72" s="5" t="inlineStr"/>
-      <c r="F72" s="6" t="inlineStr"/>
-      <c r="G72" s="6" t="inlineStr"/>
-      <c r="H72" s="4" t="inlineStr">
+      <c r="D72" s="6" t="inlineStr"/>
+      <c r="E72" s="6" t="inlineStr"/>
+      <c r="F72" s="7" t="inlineStr"/>
+      <c r="G72" s="7" t="inlineStr"/>
+      <c r="H72" s="8" t="inlineStr"/>
+      <c r="I72" s="5" t="inlineStr">
         <is>
           <t>9:15 PM INTRO: Sophie Kluge</t>
         </is>
